--- a/stories/arbres/TREE-SAN-001.xlsx
+++ b/stories/arbres/TREE-SAN-001.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est l'heure de manger. Lina a faim. Maman est dans la cuisine. Papa est là aussi. Dans l'assiette, il y a un légume. Maman dit : tu peux goûter. Une petite portion. Puis tu nommes le goût. Lina écoute.</t>
+          <t>C'est l'heure de manger. Lina a faim. Maman est dans la cuisine. Papa est là aussi. Dans l'assiette, il y a un légume. Tu peux goûter. Une petite portion. Puis tu nommes le goût. Lina écoute.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est l'heure de manger. Lina a faim. Maman est dans la cuisine. Papa est là aussi. Dans l'assiette, il y a un légume.
+maman|Tu peux goûter.
+narrateur|Une petite portion. Puis tu nommes le goût. Lina écoute.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1515,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1544,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lina entre dans la cuisine. Ça sent la soupe. Elle s'assoit à table, près de maman. Une carotte orange est dans l'assiette. Maman dit : goûte une petite portion. Lina prend une petite bouchée. C'est un peu sucré. Lina nomme le goût : c'est sucré, maman.</t>
+          <t>Lina entre dans la cuisine. Ça sent la soupe. Elle s'assoit à table, près de maman. Une carotte orange est dans l'assiette. Goûte une petite portion. Lina prend une petite bouchée. C'est un peu sucré. Lina nomme le goût : c'est sucré, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1682,13 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lina entre dans la cuisine. Ça sent la soupe. Elle s'assoit à table, près de maman. Une carotte orange est dans l'assiette.
+maman|Goûte une petite portion.
+narrateur|Lina prend une petite bouchée. C'est un peu sucré. Lina nomme le goût : c'est sucré, maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1869,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Lina prend une petite bouchée. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2042,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a goûté. Elle a nommé le goût. Une petite portion, c'est bien. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2237,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la carotte, le petit pois, ou la courgette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2215,7 +2266,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Maman coupe un tout petit bout de carotte. Lina goûte une petite portion. C'est croquant. Elle nomme le goût : sucré. Papa dit : merci d'avoir goûté.</t>
+          <t>Maman coupe un tout petit bout de carotte. Lina goûte une petite portion. C'est croquant. Elle nomme le goût : sucré. Merci d'avoir goûté.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2353,6 +2404,12 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Maman coupe un tout petit bout de carotte. Lina goûte une petite portion. C'est croquant. Elle nomme le goût : sucré.
+papa|Merci d'avoir goûté.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2547,6 +2604,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2571,7 +2633,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Tom s'assoit près de Lina. Lina dit : la carotte est sucrée. Elle a goûté une petite portion. Elle a nommé le goût. Tom tapote la table. Ils rient.</t>
+          <t>Tom s'assoit près de Lina. La carotte est sucrée. Elle a goûté une petite portion. Elle a nommé le goût. Tom tapote la table. Ils rient.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2709,6 +2771,12 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'assoit près de Lina.
+enfant-f|La carotte est sucrée. Elle a goûté une petite portion. Elle a nommé le goût. Tom tapote la table. Ils rient.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2871,6 +2939,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2895,7 +2968,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Léa écoute. Lina dit : c'est sucré. Elle a goûté une petite portion. Elle nomme le goût. Léa sourit. Maman verse de l'eau.</t>
+          <t>Léa écoute. C'est sucré. Elle a goûté une petite portion. Elle nomme le goût. Léa sourit. Maman verse de l'eau.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3033,6 +3106,12 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Léa écoute.
+enfant-f|C'est sucré. Elle a goûté une petite portion. Elle nomme le goût. Léa sourit. Maman verse de l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3195,6 +3274,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3219,7 +3303,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sami regarde la carotte orange. Lina dit : j'ai goûté. C'est sucré. Une petite portion. Elle nomme le goût. Sami dit merci à maman.</t>
+          <t>Sami regarde la carotte orange. J'ai goûté. C'est sucré. Une petite portion. Elle nomme le goût. Sami dit merci à maman.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3357,6 +3441,13 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sami regarde la carotte orange.
+enfant-f|J'ai goûté. C'est sucré.
+narrateur|Une petite portion. Elle nomme le goût. Sami dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3519,6 +3610,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3543,7 +3639,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Papa pose un petit pois vert. Il est tout rond. Lina goûte une petite portion. C'est doux. Elle nomme le goût : doux. Maman dit : une petite bouchée, c'est assez.</t>
+          <t>Papa pose un petit pois vert. Il est tout rond. Lina goûte une petite portion. C'est doux. Elle nomme le goût : doux. Une petite bouchée, c'est assez.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3681,6 +3777,12 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Papa pose un petit pois vert. Il est tout rond. Lina goûte une petite portion. C'est doux. Elle nomme le goût : doux.
+maman|Une petite bouchée, c'est assez.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3873,6 +3975,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4037,6 +4144,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Tom compte : un petit pois. Lina goûte. Elle nomme le goût : doux. Une petite portion. Tom applaudit tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4199,6 +4311,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4361,6 +4478,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Léa chuchote : c'est petit. Lina goûte une petite portion. Elle nomme le goût. Léa goûte aussi, si elle veut. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4523,6 +4645,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4685,6 +4812,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rit : c'est rond. Lina a goûté. Elle a nommé le goût. Une petite portion. Sami range sa cuillère.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4847,6 +4979,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5009,6 +5146,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Maman donne un cube de courgette. Il est tendre. Lina goûte une petite portion. C'est doux, un peu tiède. Elle nomme le goût à maman. Papa hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5203,6 +5345,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5227,7 +5374,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Tom dit : c'est vert. Lina dit : c'est doux. Elle a goûté une petite portion. Elle a nommé le goût. Ils restent à table.</t>
+          <t>C'est vert. C'est doux. Elle a goûté une petite portion. Elle a nommé le goût. Ils restent à table.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5365,6 +5512,12 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>enfant-m|C'est vert.
+enfant-f|C'est doux. Elle a goûté une petite portion. Elle a nommé le goût. Ils restent à table.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5527,6 +5680,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5551,7 +5709,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Léa touche l'assiette, tout doux. Lina goûte. Elle nomme le goût. Une petite portion. Léa dit : merci maman.</t>
+          <t>Léa touche l'assiette, tout doux. Lina goûte. Elle nomme le goût. Une petite portion. Merci maman.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5689,6 +5847,12 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Léa touche l'assiette, tout doux. Lina goûte. Elle nomme le goût. Une petite portion.
+enfant-f|Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5851,6 +6015,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6013,6 +6182,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sami souffle sur le cube. Lina goûte une petite portion. Elle nomme le goût : doux. Sami pose sa serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6175,6 +6349,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6199,7 +6378,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Lina va au jardin avec maman. Le soleil est chaud. Une petite tomate rouge brille. Maman la lave. Maman dit : goûte une petite portion. Lina croque un tout petit bout. C'est juteux. Elle nomme le goût : c'est juteux, maman.</t>
+          <t>Lina va au jardin avec maman. Le soleil est chaud. Une petite tomate rouge brille. Maman la lave. Goûte une petite portion. Lina croque un tout petit bout. C'est juteux. Elle nomme le goût : c'est juteux, maman.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6337,6 +6516,13 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va au jardin avec maman. Le soleil est chaud. Une petite tomate rouge brille. Maman la lave.
+maman|Goûte une petite portion.
+narrateur|Lina croque un tout petit bout. C'est juteux. Elle nomme le goût : c'est juteux, maman.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6513,6 +6699,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Lina goûte la tomate. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -6681,6 +6872,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a goûté au jardin. Elle a nommé le goût. Une petite portion, c'est déjà bien.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6871,6 +7067,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la tomate, le radis, ou la salade.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7033,6 +7234,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lina cueille une tomate cerise. Papa est près du bac. Elle goûte une petite portion. C'est chaud du soleil. Elle nomme le goût : sucré et juteux.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7227,6 +7433,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7251,7 +7462,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Tom sent la tomate. Lina dit : c'est sucré. Elle a goûté une petite portion. Elle nomme le goût. Une abeille passe loin.</t>
+          <t>Tom sent la tomate. C'est sucré. Elle a goûté une petite portion. Elle nomme le goût. Une abeille passe loin.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7389,6 +7600,13 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Tom sent la tomate.
+enfant-f|C'est sucré. Elle a goûté une petite portion. Elle nomme le goût.
+narrateur|Une abeille passe loin.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7551,6 +7769,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7575,7 +7798,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Léa s'assoit dans l'herbe. Lina goûte. Elle nomme le goût. Une petite portion. Léa dit : c'est rouge.</t>
+          <t>Léa s'assoit dans l'herbe. Lina goûte. Elle nomme le goût. Une petite portion. C'est rouge.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7713,6 +7936,12 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'assoit dans l'herbe. Lina goûte. Elle nomme le goût. Une petite portion.
+enfant-f|C'est rouge.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7875,6 +8104,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8037,6 +8271,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sami tient l'arrosoir. Lina a goûté. Elle a nommé le goût. Une petite portion. Ils rentrent avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8199,6 +8438,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8361,6 +8605,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Maman tire un petit radis. Il pique un peu le nez. Lina goûte une petite portion. C'est vif. Elle nomme le goût : un peu piquant. Papa rit doucement.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8555,6 +8804,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8579,7 +8833,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Tom ouvre les yeux grand. Lina dit : ça pique un peu. Elle a goûté une petite portion. Elle nomme le goût. Tom dit : merci.</t>
+          <t>Tom ouvre les yeux grand. Ça pique un peu. Elle a goûté une petite portion. Elle nomme le goût. Merci.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8717,6 +8971,13 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Tom ouvre les yeux grand.
+enfant-f|Ça pique un peu. Elle a goûté une petite portion. Elle nomme le goût.
+enfant-m|Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8879,6 +9140,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9041,6 +9307,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Léa boit une gorgée d'eau. Lina a goûté. Elle a nommé le goût. Une petite portion. Léa s'essuie la bouche.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9203,6 +9474,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9365,6 +9641,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sami sent le radis. Lina goûte une petite portion. Elle nomme le goût. Sami range le panier.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9527,6 +9808,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9551,7 +9837,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Papa cueille une feuille de salade. Elle est fraîche. Lina goûte une petite portion. C'est croquant. Elle nomme le goût : frais. Maman dit : bien dit.</t>
+          <t>Papa cueille une feuille de salade. Elle est fraîche. Lina goûte une petite portion. C'est croquant. Elle nomme le goût : frais. Bien dit.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9689,6 +9975,12 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Papa cueille une feuille de salade. Elle est fraîche. Lina goûte une petite portion. C'est croquant. Elle nomme le goût : frais.
+maman|Bien dit.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9883,6 +10175,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9907,7 +10204,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Tom touche la feuille. Lina dit : c'est frais. Elle a goûté une petite portion. Elle nomme le goût. Le vent est doux.</t>
+          <t>Tom touche la feuille. C'est frais. Elle a goûté une petite portion. Elle nomme le goût. Le vent est doux.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10045,6 +10342,13 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Tom touche la feuille.
+enfant-f|C'est frais. Elle a goûté une petite portion. Elle nomme le goût.
+narrateur|Le vent est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10207,6 +10511,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10369,6 +10678,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Léa met la feuille dans le panier. Lina a goûté. Elle a nommé le goût. Une petite portion. Elles marchent vers la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10531,6 +10845,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10555,7 +10874,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Sami écoute. Lina goûte une petite portion. Elle nomme le goût : croquant. Sami dit : moi aussi, une petite bouchée.</t>
+          <t>Sami écoute. Lina goûte une petite portion. Elle nomme le goût : croquant. Moi aussi, une petite bouchée.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10693,6 +11012,12 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sami écoute. Lina goûte une petite portion. Elle nomme le goût : croquant.
+enfant-m|Moi aussi, une petite bouchée.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10855,6 +11180,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10879,7 +11209,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Lina est dans sa chambre. Maman apporte un petit plateau. Il y a un bâtonnet de concombre. Maman dit : tu peux goûter une petite portion. Lina croque. C'est froid et frais. Elle nomme le goût : c'est frais, maman.</t>
+          <t>Lina est dans sa chambre. Maman apporte un petit plateau. Il y a un bâtonnet de concombre. Tu peux goûter une petite portion. Lina croque. C'est froid et frais. Elle nomme le goût : c'est frais, maman.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11017,6 +11347,13 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Lina est dans sa chambre. Maman apporte un petit plateau. Il y a un bâtonnet de concombre.
+maman|Tu peux goûter une petite portion.
+narrateur|Lina croque. C'est froid et frais. Elle nomme le goût : c'est frais, maman.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11193,6 +11530,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Lina nomme le goût. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -11361,6 +11703,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Même dans la chambre, Lina a goûté. Elle a nommé le goût. Une petite portion suffit.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11551,6 +11898,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le concombre, le poivron, ou le maïs.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11713,6 +12065,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Le concombre est froid. Lina goûte une petite portion. Ça croque. Elle nomme le goût : frais. Papa pose le doudou à côté, tout sage.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11907,6 +12264,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11931,7 +12293,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Tom s'assoit sur le tapis. Lina dit : c'est frais. Elle a goûté une petite portion. Elle nomme le goût. Tom pose le plateau.</t>
+          <t>Tom s'assoit sur le tapis. C'est frais. Elle a goûté une petite portion. Elle nomme le goût. Tom pose le plateau.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12069,6 +12431,12 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'assoit sur le tapis.
+enfant-f|C'est frais. Elle a goûté une petite portion. Elle nomme le goût. Tom pose le plateau.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12231,6 +12599,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12255,7 +12628,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Léa tient le doudou. Lina goûte. Elle nomme le goût. Une petite portion. Léa dit : c'est vert.</t>
+          <t>Léa tient le doudou. Lina goûte. Elle nomme le goût. Une petite portion. C'est vert.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12393,6 +12766,12 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Léa tient le doudou. Lina goûte. Elle nomme le goût. Une petite portion.
+enfant-f|C'est vert.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12555,6 +12934,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12717,6 +13101,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sami écoute près de la fenêtre. Lina a goûté. Elle a nommé le goût. Une petite portion. Ils rangent le plateau.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12879,6 +13268,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12903,7 +13297,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Maman offre un tout petit morceau de poivron. Il est rouge. Lina goûte une petite portion. C'est un peu sucré. Elle nomme le goût. Papa dit : tu as dit le goût. Merci.</t>
+          <t>Maman offre un tout petit morceau de poivron. Il est rouge. Lina goûte une petite portion. C'est un peu sucré. Elle nomme le goût. Tu as dit le goût. Merci.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13041,6 +13435,12 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Maman offre un tout petit morceau de poivron. Il est rouge. Lina goûte une petite portion. C'est un peu sucré. Elle nomme le goût.
+papa|Tu as dit le goût. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13235,6 +13635,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13259,7 +13664,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Tom dit : c'est rouge. Lina dit : c'est sucré. Elle a goûté une petite portion. Elle nomme le goût. Ils sourient.</t>
+          <t>C'est rouge. C'est sucré. Elle a goûté une petite portion. Elle nomme le goût. Ils sourient.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13397,6 +13802,12 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>enfant-m|C'est rouge.
+enfant-f|C'est sucré. Elle a goûté une petite portion. Elle nomme le goût. Ils sourient.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13559,6 +13970,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13721,6 +14137,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Léa sent le poivron. Lina goûte une petite portion. Elle nomme le goût. Léa tapote le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13883,6 +14304,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14045,6 +14471,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sami chuchote. Lina a goûté. Elle a nommé le goût. Une petite portion. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14207,6 +14638,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14231,7 +14667,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Papa montre un grain de maïs. Il est jaune. Lina goûte une petite portion. C'est doux. Elle nomme le goût : doux. Maman dit : une petite bouchée, c'est bien.</t>
+          <t>Papa montre un grain de maïs. Il est jaune. Lina goûte une petite portion. C'est doux. Elle nomme le goût : doux. Une petite bouchée, c'est bien.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14369,6 +14805,12 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Papa montre un grain de maïs. Il est jaune. Lina goûte une petite portion. C'est doux. Elle nomme le goût : doux.
+maman|Une petite bouchée, c'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14561,6 +15003,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14725,6 +15172,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rit : c'est jaune. Lina goûte. Elle nomme le goût. Une petite portion. Tom range le grain.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14887,6 +15339,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14911,7 +15368,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Léa s'allonge un peu. Lina a goûté une petite portion. Elle a nommé le goût. Léa dit : c'est doux.</t>
+          <t>Léa s'allonge un peu. Lina a goûté une petite portion. Elle a nommé le goût. C'est doux.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15049,6 +15506,12 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'allonge un peu. Lina a goûté une petite portion. Elle a nommé le goût.
+enfant-f|C'est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15211,6 +15674,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15373,6 +15841,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sami pose le plateau. Lina a goûté. Elle nomme le goût. Une petite portion. Maman baisse le store.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15535,6 +16008,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15553,7 +16031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15626,6 +16104,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-001.xlsx
+++ b/stories/arbres/TREE-SAN-001.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Une petite portion. Puis tu nommes le goût. Lina écoute.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1520,6 +1526,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1689,6 +1696,7 @@
 narrateur|Lina prend une petite bouchée. C'est un peu sucré. Lina nomme le goût : c'est sucré, maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1876,6 +1884,7 @@
           <t>narrateur|Lina prend une petite bouchée. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2047,6 +2056,7 @@
           <t>narrateur|Lina a goûté. Elle a nommé le goût. Une petite portion, c'est bien. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2242,6 +2252,7 @@
           <t>narrateur|On peut prendre la carotte, le petit pois, ou la courgette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2410,6 +2421,7 @@
 papa|Merci d'avoir goûté.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2609,6 +2621,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2777,6 +2790,7 @@
 enfant-f|La carotte est sucrée. Elle a goûté une petite portion. Elle a nommé le goût. Tom tapote la table. Ils rient.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2944,6 +2958,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3112,6 +3127,7 @@
 enfant-f|C'est sucré. Elle a goûté une petite portion. Elle nomme le goût. Léa sourit. Maman verse de l'eau.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3279,6 +3295,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3448,6 +3465,7 @@
 narrateur|Une petite portion. Elle nomme le goût. Sami dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3615,6 +3633,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3783,6 +3802,7 @@
 maman|Une petite bouchée, c'est assez.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3982,6 +4002,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4149,6 +4170,7 @@
           <t>narrateur|Tom compte : un petit pois. Lina goûte. Elle nomme le goût : doux. Une petite portion. Tom applaudit tout doux.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4316,6 +4338,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4483,6 +4506,7 @@
           <t>narrateur|Léa chuchote : c'est petit. Lina goûte une petite portion. Elle nomme le goût. Léa goûte aussi, si elle veut. Maman est là.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4650,6 +4674,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4817,6 +4842,7 @@
           <t>narrateur|Sami rit : c'est rond. Lina a goûté. Elle a nommé le goût. Une petite portion. Sami range sa cuillère.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4984,6 +5010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5151,6 +5178,7 @@
           <t>narrateur|Maman donne un cube de courgette. Il est tendre. Lina goûte une petite portion. C'est doux, un peu tiède. Elle nomme le goût à maman. Papa hoche la tête.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5350,6 +5378,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5518,6 +5547,7 @@
 enfant-f|C'est doux. Elle a goûté une petite portion. Elle a nommé le goût. Ils restent à table.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5685,6 +5715,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5853,6 +5884,7 @@
 enfant-f|Merci maman.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6020,6 +6052,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6187,6 +6220,7 @@
           <t>narrateur|Sami souffle sur le cube. Lina goûte une petite portion. Elle nomme le goût : doux. Sami pose sa serviette.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6354,6 +6388,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6523,6 +6558,7 @@
 narrateur|Lina croque un tout petit bout. C'est juteux. Elle nomme le goût : c'est juteux, maman.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6706,6 +6742,7 @@
           <t>narrateur|Lina goûte la tomate. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6877,6 +6914,7 @@
           <t>narrateur|Lina a goûté au jardin. Elle a nommé le goût. Une petite portion, c'est déjà bien.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7072,6 +7110,7 @@
           <t>narrateur|On peut prendre la tomate, le radis, ou la salade.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7239,6 +7278,7 @@
           <t>narrateur|Lina cueille une tomate cerise. Papa est près du bac. Elle goûte une petite portion. C'est chaud du soleil. Elle nomme le goût : sucré et juteux.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7438,6 +7478,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7607,6 +7648,7 @@
 narrateur|Une abeille passe loin.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7774,6 +7816,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7942,6 +7985,7 @@
 enfant-f|C'est rouge.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8109,6 +8153,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8276,6 +8321,7 @@
           <t>narrateur|Sami tient l'arrosoir. Lina a goûté. Elle a nommé le goût. Une petite portion. Ils rentrent avec maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8443,6 +8489,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8610,6 +8657,7 @@
           <t>narrateur|Maman tire un petit radis. Il pique un peu le nez. Lina goûte une petite portion. C'est vif. Elle nomme le goût : un peu piquant. Papa rit doucement.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8809,6 +8857,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8978,6 +9027,7 @@
 enfant-m|Merci.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9145,6 +9195,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9312,6 +9363,7 @@
           <t>narrateur|Léa boit une gorgée d'eau. Lina a goûté. Elle a nommé le goût. Une petite portion. Léa s'essuie la bouche.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9479,6 +9531,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9646,6 +9699,7 @@
           <t>narrateur|Sami sent le radis. Lina goûte une petite portion. Elle nomme le goût. Sami range le panier.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9813,6 +9867,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9981,6 +10036,7 @@
 maman|Bien dit.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10180,6 +10236,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10349,6 +10406,7 @@
 narrateur|Le vent est doux.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10516,6 +10574,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10683,6 +10742,7 @@
           <t>narrateur|Léa met la feuille dans le panier. Lina a goûté. Elle a nommé le goût. Une petite portion. Elles marchent vers la maison.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10850,6 +10910,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11018,6 +11079,7 @@
 enfant-m|Moi aussi, une petite bouchée.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11185,6 +11247,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11354,6 +11417,7 @@
 narrateur|Lina croque. C'est froid et frais. Elle nomme le goût : c'est frais, maman.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11537,6 +11601,7 @@
           <t>narrateur|Lina nomme le goût. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11708,6 +11773,7 @@
           <t>narrateur|Même dans la chambre, Lina a goûté. Elle a nommé le goût. Une petite portion suffit.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11903,6 +11969,7 @@
           <t>narrateur|On peut prendre le concombre, le poivron, ou le maïs.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12070,6 +12137,7 @@
           <t>narrateur|Le concombre est froid. Lina goûte une petite portion. Ça croque. Elle nomme le goût : frais. Papa pose le doudou à côté, tout sage.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12269,6 +12337,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12437,6 +12506,7 @@
 enfant-f|C'est frais. Elle a goûté une petite portion. Elle nomme le goût. Tom pose le plateau.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12604,6 +12674,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12772,6 +12843,7 @@
 enfant-f|C'est vert.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12939,6 +13011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13106,6 +13179,7 @@
           <t>narrateur|Sami écoute près de la fenêtre. Lina a goûté. Elle a nommé le goût. Une petite portion. Ils rangent le plateau.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13273,6 +13347,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13441,6 +13516,7 @@
 papa|Tu as dit le goût. Merci.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13640,6 +13716,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13808,6 +13885,7 @@
 enfant-f|C'est sucré. Elle a goûté une petite portion. Elle nomme le goût. Ils sourient.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13975,6 +14053,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14142,6 +14221,7 @@
           <t>narrateur|Léa sent le poivron. Lina goûte une petite portion. Elle nomme le goût. Léa tapote le doudou.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14309,6 +14389,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14476,6 +14557,7 @@
           <t>narrateur|Sami chuchote. Lina a goûté. Elle a nommé le goût. Une petite portion. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14643,6 +14725,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14811,6 +14894,7 @@
 maman|Une petite bouchée, c'est bien.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15010,6 +15094,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15177,6 +15262,7 @@
           <t>narrateur|Tom rit : c'est jaune. Lina goûte. Elle nomme le goût. Une petite portion. Tom range le grain.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15344,6 +15430,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15512,6 +15599,7 @@
 enfant-f|C'est doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15679,6 +15767,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15846,6 +15935,7 @@
           <t>narrateur|Sami pose le plateau. Lina a goûté. Elle nomme le goût. Une petite portion. Maman baisse le store.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16013,6 +16103,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16031,7 +16122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16111,6 +16202,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16125,7 +16230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16312,6 +16417,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
